--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N43_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N43_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>37.32571000588278</v>
+        <v>6.065427875955953</v>
       </c>
       <c r="D2" t="n">
-        <v>37.15007756264019</v>
+        <v>6.036887603929031</v>
       </c>
       <c r="E2" t="n">
-        <v>8.137537926579727</v>
+        <v>1.322349913069206</v>
       </c>
       <c r="F2" t="n">
-        <v>9.226637132345354</v>
+        <v>1.49932853400612</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>13.85371495561366</v>
+        <v>2.251228680287219</v>
       </c>
       <c r="D3" t="n">
-        <v>13.44079154902849</v>
+        <v>2.18412862671713</v>
       </c>
       <c r="E3" t="n">
-        <v>8.137537926579727</v>
+        <v>1.322349913069206</v>
       </c>
       <c r="F3" t="n">
-        <v>9.226637132345354</v>
+        <v>1.49932853400612</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.93473365090101</v>
+        <v>4.051894218271413</v>
       </c>
       <c r="D4" t="n">
-        <v>24.54398755344335</v>
+        <v>3.988397977434545</v>
       </c>
       <c r="E4" t="n">
-        <v>8.137537926579727</v>
+        <v>1.322349913069206</v>
       </c>
       <c r="F4" t="n">
-        <v>9.226637132345354</v>
+        <v>1.49932853400612</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>29.12825893106148</v>
+        <v>4.73334207629749</v>
       </c>
       <c r="D5" t="n">
-        <v>28.69052780963805</v>
+        <v>4.662210769066183</v>
       </c>
       <c r="E5" t="n">
-        <v>8.137537926579727</v>
+        <v>1.322349913069206</v>
       </c>
       <c r="F5" t="n">
-        <v>9.226637132345354</v>
+        <v>1.49932853400612</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>23.96665288933217</v>
+        <v>3.894581094516478</v>
       </c>
       <c r="D6" t="n">
-        <v>23.57061258262648</v>
+        <v>3.830224544676804</v>
       </c>
       <c r="E6" t="n">
-        <v>8.137537926579727</v>
+        <v>1.322349913069206</v>
       </c>
       <c r="F6" t="n">
-        <v>9.226637132345354</v>
+        <v>1.49932853400612</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>32.05425771942129</v>
+        <v>5.208816879405959</v>
       </c>
       <c r="D7" t="n">
-        <v>32.05758346281894</v>
+        <v>5.209357312708078</v>
       </c>
       <c r="E7" t="n">
-        <v>8.137537926579727</v>
+        <v>1.322349913069206</v>
       </c>
       <c r="F7" t="n">
-        <v>9.226637132345354</v>
+        <v>1.49932853400612</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>44.95988025760362</v>
+        <v>7.305980541860589</v>
       </c>
       <c r="D8" t="n">
-        <v>40.91025702610047</v>
+        <v>6.647916766741326</v>
       </c>
       <c r="E8" t="n">
-        <v>8.137537926579727</v>
+        <v>1.322349913069206</v>
       </c>
       <c r="F8" t="n">
-        <v>9.226637132345354</v>
+        <v>1.49932853400612</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>33.12992604238188</v>
+        <v>5.383612981887055</v>
       </c>
       <c r="D9" t="n">
-        <v>32.90653384347458</v>
+        <v>5.347311749564621</v>
       </c>
       <c r="E9" t="n">
-        <v>8.137537926579727</v>
+        <v>1.322349913069206</v>
       </c>
       <c r="F9" t="n">
-        <v>9.226637132345354</v>
+        <v>1.49932853400612</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>18.92760050434961</v>
+        <v>3.075735081956811</v>
       </c>
       <c r="D10" t="n">
-        <v>19.130447139471</v>
+        <v>3.108697660164038</v>
       </c>
       <c r="E10" t="n">
-        <v>8.137537926579727</v>
+        <v>1.322349913069206</v>
       </c>
       <c r="F10" t="n">
-        <v>9.226637132345354</v>
+        <v>1.49932853400612</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>43.02360404420247</v>
+        <v>6.991335657182902</v>
       </c>
       <c r="D11" t="n">
-        <v>45.97490317981855</v>
+        <v>7.470921766720515</v>
       </c>
       <c r="E11" t="n">
-        <v>8.137537926579727</v>
+        <v>1.322349913069206</v>
       </c>
       <c r="F11" t="n">
-        <v>9.226637132345354</v>
+        <v>1.49932853400612</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>28.55875613205517</v>
+        <v>4.640797871458965</v>
       </c>
       <c r="D12" t="n">
-        <v>12.90241314983996</v>
+        <v>2.096642136848994</v>
       </c>
       <c r="E12" t="n">
-        <v>8.137537926579727</v>
+        <v>1.322349913069206</v>
       </c>
       <c r="F12" t="n">
-        <v>9.226637132345354</v>
+        <v>1.49932853400612</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>27.9433619872164</v>
+        <v>4.540796322922664</v>
       </c>
       <c r="D13" t="n">
-        <v>28.49102997434434</v>
+        <v>4.629792370830955</v>
       </c>
       <c r="E13" t="n">
-        <v>8.137537926579727</v>
+        <v>1.322349913069206</v>
       </c>
       <c r="F13" t="n">
-        <v>9.226637132345354</v>
+        <v>1.49932853400612</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>30.01563740149027</v>
+        <v>4.877541077742168</v>
       </c>
       <c r="D14" t="n">
-        <v>29.68734603054891</v>
+        <v>4.824193729964198</v>
       </c>
       <c r="E14" t="n">
-        <v>8.137537926579727</v>
+        <v>1.322349913069206</v>
       </c>
       <c r="F14" t="n">
-        <v>9.226637132345354</v>
+        <v>1.49932853400612</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>33.70392718745271</v>
+        <v>5.476888167961066</v>
       </c>
       <c r="D15" t="n">
-        <v>33.75005082186344</v>
+        <v>5.484383258552809</v>
       </c>
       <c r="E15" t="n">
-        <v>8.137537926579727</v>
+        <v>1.322349913069206</v>
       </c>
       <c r="F15" t="n">
-        <v>9.226637132345354</v>
+        <v>1.49932853400612</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
